--- a/data/data-template.xlsx
+++ b/data/data-template.xlsx
@@ -2,13 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10308"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hmgu-my.sharepoint.com/personal/theresa_willem_helmholtz-munich_de/Documents/Voucher - Sustainable AI/Data/Survey/Working scripts/Github/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{FD387A7E-9F35-9542-B313-B7E1572FD3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5719509B-BE11-7B41-94DB-A4DF4F4B83AD}"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{F7A97B43-BDC9-3547-9C74-FBDD6F4EB653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4740" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
